--- a/光伏配储项目/电价数据/2026/珍珠湾开关站.xlsx
+++ b/光伏配储项目/电价数据/2026/珍珠湾开关站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.6960299999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5635</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44576</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44018</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4379</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45471</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42344</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42428</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41307</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26101</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.20164</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25038</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07067</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.05862</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.02281</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03815</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.03749</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.00831</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.04516</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08551</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02153</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01219</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14466</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21263</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23503</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18409</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.02726</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01023</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.10403</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11551</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.16432</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.21503</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.15459</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.13097</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.11081</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.17768</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.21744</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.43689</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52179</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.46686</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7289099999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6094400000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.49707</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.48024</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.00634</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.56336</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5301</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.20127</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.48776</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.49185</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.58787</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5462</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42096</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.61449</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.40984</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.74172</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.97341</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79935</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53704</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52404</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50666</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50466</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50241</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47439</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5168200000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.62958</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72148</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08155</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.25628</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26911</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.23181</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.58914</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.09965</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27254</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.26503</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.23735</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.5651799999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.03123</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.22257</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.16114</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.22432</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.22821</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.2311</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25002</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.22661</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.41858</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.22885</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68653</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7942400000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78704</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.21292</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.80306</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43542</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.58996</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43877</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33312</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51552</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46692</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40134</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44858</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47402</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44824</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44261</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27393</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.13017</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27423</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24891</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.23586</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.25532</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.06086</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.20513</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.13507</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.19431</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.18256</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24442</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.26184</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.21488</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.17588</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.04744</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.2721</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.46111</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.48996</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.26417</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.27154</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3434</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47037</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26306</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.20792</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12625</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.12009</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26552</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22623</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44588</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.20034</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06434000000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.25803</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.20603</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04429</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.008840000000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03478</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.06598999999999999</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.10124</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.25114</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.1939</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.22266</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.18113</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.23066</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16125</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25138</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.28962</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.26615</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48429</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29102</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28386</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.2830299999999999</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04015999999999999</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03993</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04296</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04617</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04454</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04657</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04201</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.0445</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04464</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04566</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04459</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04354</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04595</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04503</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04719</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04709000000000001</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04502</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04696</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22031</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04729999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05125</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05343</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00257</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14649</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09844</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41761</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04628</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04258</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03195</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04136</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10654</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03766</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.0422</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04209</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04438</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04429</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04428</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04205</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04149</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0413</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03982</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04492</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04401</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.0443</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04185</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04288</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04049000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04296</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04684000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04674</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20148</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14406</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27046</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.337</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32081</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27267</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17362</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15987</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17244</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14894</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15996</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21538</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22793</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27108</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.41921</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92318</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.89251</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31133</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.91547</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63618</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.21452</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88222</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.56577</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35906</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.05224</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5591699999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.81517</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.79728</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.79683</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87976</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8865700000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5158700000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42084</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42908</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47588</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23618</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87967</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55153</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.65078</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5455399999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50601</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44225</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59662</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60156</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6558999999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40621</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55787</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44639</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86197</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.65608</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.81199</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8481599999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41974</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.98714</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48742</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.54479</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.61287</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.41821</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.45898</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16456</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20054</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.25644</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26936</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27545</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27736</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44776</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5978300000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88967</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35055</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14047</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7073400000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6523099999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58766</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.55401</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.06265999999999999</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.56126</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.04246</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.66287</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21888</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.5400900000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26566</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.58641</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46448</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7154400000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46582</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43869</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42462</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32569</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27118</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23584</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14495</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14727</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15413</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14438</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14416</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25741</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14469</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26712</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14214</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03435</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11415</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11326</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14539</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14149</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14667</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45082</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44101</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44045</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44539</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44485</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35008</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.55016</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46975</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27232</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.26841</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.24276</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.18329</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21944</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.26625</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.21949</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.2770899999999999</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.26104</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24381</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.4456</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36055</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03845000000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25097</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25001</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07096</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.17939</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24447</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26804</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.24984</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.26912</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46936</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.73249</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45844</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40419</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30108</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28486</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28528</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.60194</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3817</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42957</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6472100000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83297</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47414</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45836</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34505</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26073</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13399</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19471</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24483</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.02262</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.11372</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.02283</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28396</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23069</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28699</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24044</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14405</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.2094</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.21685</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29095</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41622</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6491399999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61381</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6089</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46599</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6306</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47507</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7664500000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47808</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41886</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36023</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48947</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.46643</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4632</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45169</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41802</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40996</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41839</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41655</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55811</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49884</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44977</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42664</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.24234</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.26605</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.12604</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00431</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.01215</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.66614</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.11996</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.08344</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.04264</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.25679</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.00761</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48357</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50595</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50757</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.57586</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.69123</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.68968</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.6670199999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.75359</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5416299999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5215</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8173400000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75307</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60517</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65437</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48139</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47785</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47179</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.53465</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42376</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44272</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43658</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42617</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44781</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41773</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45714</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38681</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27196</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15486</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45437</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46506</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.03964</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18392</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.04474</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36404</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44379</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.2453</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23268</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23415</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2343</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24769</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.00283</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13195</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23221</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.01053</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.15991</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25614</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.00436</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14515</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15344</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.04018</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21666</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2281</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.15151</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21378</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.26155</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35227</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22648</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21654</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.17963</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.06809</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01605</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00164</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04296</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03359</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04434</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04846</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.04083</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16924</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21448</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24433</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24551</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24601</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25033</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26316</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27178</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25674</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26501</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.27964</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26739</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25464</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26629</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25066</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.17769</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05474</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.01172</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06353</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.24792</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22424</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.2241</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14301</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26921</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24297</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22123</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20552</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.18868</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21267</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22549</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16891</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22265</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.21899</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24381</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23151</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21441</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22489</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26833</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27037</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24608</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24901</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18331</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06328</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.48948</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.49765</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.54561</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.07357999999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.22635</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02236</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20171</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09268000000000001</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05475</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.008029999999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20786</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03124</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02585</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03879999999999999</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.03977</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.03193</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.08112999999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02524</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.01521</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.04694</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23547</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25303</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.20421</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32531</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.11242</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.26915</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25737</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25269</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.13794</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24305</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.11297</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25701</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26973</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.16712</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14974</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33119</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26292</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5057200000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50554</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25621</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26333</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.15991</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.25952</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27893</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.25745</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25844</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.23615</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26594</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47042</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48363</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46407</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47702</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.02985</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.43833</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47391</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43447</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.42023</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42584</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.74272</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36899</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46778</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.20057</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.15709</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23583</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17497</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26638</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46327</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.55975</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5559400000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45873</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54745</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46247</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49487</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53455</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52596</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.72962</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.77191</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5479299999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55008</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44357</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37566</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2734</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.25927</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.25953</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27527</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20925</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23365</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.15246</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.00205</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.0305</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.14007</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01407</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.12919</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01192</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04078</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02407</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23399</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.04088</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02532</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02052</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01347</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02995</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12129</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.07281</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.15598</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.18942</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.24708</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.19016</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.27016</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41711</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37846</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.80887</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.28082</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.25827</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.24858</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.21975</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.21903</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.22337</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.08638</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01028</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.00869</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.11746</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.02866</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04432</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01031</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01649</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15581</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.17874</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.03240999999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.17059</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.15511</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.18175</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.16591</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.24042</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.19757</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.26016</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.22605</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.26209</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44377</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5186000000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39287</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38632</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.52139</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25421</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.19881</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12717</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17597</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20139</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.19552</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.09995</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.05679</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.08137999999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04007</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04104</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04097</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04466</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06858</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03254</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06053</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08367000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.1403</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.16745</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10201</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18215</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.10489</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04759</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23644</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.11894</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10306</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.20915</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15639</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.18542</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.20252</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17313</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21117</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23532</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23649</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.25303</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.27913</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40762</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49449</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40693</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42997</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38411</v>
       </c>
     </row>
   </sheetData>
